--- a/artfynd/A 30943-2024 artfynd.xlsx
+++ b/artfynd/A 30943-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81754098</v>
+        <v>107655341</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>679221.1242628057</v>
+        <v>679266</v>
       </c>
       <c r="R2" t="n">
-        <v>6680346.026357971</v>
+        <v>6680331</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,31 +761,29 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Tooke</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Tooke</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Länstyrelsen Uppsala -  Inventering inför områdesskydd 2022 </t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>107655342</v>
       </c>
       <c r="B3" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679261.4028974613</v>
+        <v>679261</v>
       </c>
       <c r="R3" t="n">
-        <v>6680368.408172739</v>
+        <v>6680369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +852,9 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,21 +879,16 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Inventering inför områdesskydd 2022 - Lst Uppsala</t>
+          <t xml:space="preserve">Länstyrelsen Uppsala -  Inventering inför områdesskydd 2022 </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107655341</v>
+        <v>81754098</v>
       </c>
       <c r="B4" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,16 +896,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222002</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,7 +915,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -956,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679266.7603821077</v>
+        <v>679221</v>
       </c>
       <c r="R4" t="n">
-        <v>6680330.348868889</v>
+        <v>6680346</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,20 +971,122 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Daniel Tooke</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Tooke</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107655343</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skomakarmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>679286</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6680380</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Greensway AB</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Inventering inför områdesskydd 2022 - Lst Uppsala</t>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Länstyrelsen Uppsala -  Inventering inför områdesskydd 2022 </t>
         </is>
       </c>
     </row>
